--- a/assets/excel/customer_attachment_info.xlsx
+++ b/assets/excel/customer_attachment_info.xlsx
@@ -35,7 +35,7 @@
     <t>电话号码</t>
   </si>
   <si>
-    <t>文件名</t>
+    <t>文件类型</t>
   </si>
   <si>
     <t>文件存储路径</t>
@@ -57,7 +57,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -70,6 +70,13 @@
       <sz val="10"/>
       <color indexed="9"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
@@ -547,159 +554,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1248,7 +1258,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">

--- a/assets/excel/customer_attachment_info.xlsx
+++ b/assets/excel/customer_attachment_info.xlsx
@@ -27,15 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>客户编号</t>
   </si>
   <si>
     <t>电话号码</t>
-  </si>
-  <si>
-    <t>文件类型</t>
   </si>
   <si>
     <t>文件存储路径</t>
@@ -57,7 +54,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -70,13 +67,6 @@
       <sz val="10"/>
       <color indexed="9"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
@@ -557,159 +547,156 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1245,20 +1232,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="6" width="16.7211538461538" customWidth="1"/>
+    <col min="1" max="5" width="16.7211538461538" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1266,9 +1253,6 @@
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" ht="14" customHeight="1"/>

--- a/assets/excel/customer_attachment_info.xlsx
+++ b/assets/excel/customer_attachment_info.xlsx
@@ -27,12 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>客户编号</t>
   </si>
   <si>
     <t>电话号码</t>
+  </si>
+  <si>
+    <t>文件名</t>
   </si>
   <si>
     <t>文件存储路径</t>
@@ -54,7 +57,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -67,6 +70,13 @@
       <sz val="10"/>
       <color indexed="9"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
@@ -547,156 +557,159 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1232,20 +1245,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="16.7211538461538" customWidth="1"/>
+    <col min="1" max="6" width="16.7211538461538" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1253,6 +1266,9 @@
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" ht="14" customHeight="1"/>
